--- a/backend/workspace/inspection_log.xlsx
+++ b/backend/workspace/inspection_log.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inspection Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,79 +418,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Valve ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Severity</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Joint A-12</t>
+          <t>V-101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Minor corrosion</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Trail Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Generated By</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>qwen2.5:1.5b-instruct (local, offline)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Valve B-7</t>
+          <t>Task Type</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>No issues</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>document</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pump C-3</t>
+          <t>Timestamp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Worn seal</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>2026-08-28T07:11:11.437838</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Source Document(s)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SOP_Valve_Maintenance_Rev3.txt (SHA-256: f3f1507a30e8c32b...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Network Status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Verified offline — zero external calls during generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sovereign Workbench v1.0</t>
         </is>
       </c>
     </row>
